--- a/database/smart_perlis_powerbi_1000_12_destinations.xlsx
+++ b/database/smart_perlis_powerbi_1000_12_destinations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\smartperlis\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6584119C-C2C6-4882-A3EB-520654743DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFDC712-1B00-488D-9D18-41679083E6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Destinations" sheetId="1" r:id="rId1"/>
@@ -4637,7 +4637,7 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
@@ -24875,9 +24875,9 @@
   <dimension ref="A1:E1001"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
@@ -41910,8 +41910,8 @@
   <dimension ref="A1:E1001"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
@@ -61262,8 +61262,9 @@
   <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
